--- a/artfynd/A 15891-2026 artfynd.xlsx
+++ b/artfynd/A 15891-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132220860</v>
       </c>
       <c r="B2" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132220876</v>
       </c>
       <c r="B3" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>132220852</v>
       </c>
       <c r="B4" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>132220864</v>
       </c>
       <c r="B5" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>132220903</v>
       </c>
       <c r="B6" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>132220808</v>
       </c>
       <c r="B7" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,13 +1286,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586996</v>
+        <v>586998</v>
       </c>
       <c r="R7" t="n">
-        <v>6432766</v>
+        <v>6432773</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>132398180</v>
       </c>
       <c r="B8" t="n">
-        <v>58629</v>
+        <v>58631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>132398210</v>
       </c>
       <c r="B9" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 15891-2026 artfynd.xlsx
+++ b/artfynd/A 15891-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,6 +1588,760 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132477502</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 15891, Edsbruk, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>586997</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6432759</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132477732</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 15891, Edsbruk, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>586983</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6432888</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132477770</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 15891, Edsbruk, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>586949</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6432879</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132477689</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 15891, Edsbruk, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>586973</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6432791</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132477468</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 15891, Edsbruk, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>586994</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6432750</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132477425</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 15891, Edsbruk, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>587005</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6432756</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132477335</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 15891, Edsbruk, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>586990</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6432777</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15891-2026 artfynd.xlsx
+++ b/artfynd/A 15891-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132220860</v>
       </c>
       <c r="B2" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132220876</v>
       </c>
       <c r="B3" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>132220852</v>
       </c>
       <c r="B4" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>132220864</v>
       </c>
       <c r="B5" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>132220903</v>
       </c>
       <c r="B6" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>132220808</v>
       </c>
       <c r="B7" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>132398180</v>
       </c>
       <c r="B8" t="n">
-        <v>58631</v>
+        <v>58632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>132398210</v>
       </c>
       <c r="B9" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>132477502</v>
       </c>
       <c r="B10" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>132477732</v>
       </c>
       <c r="B11" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>132477770</v>
       </c>
       <c r="B12" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>132477689</v>
       </c>
       <c r="B13" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>132477468</v>
       </c>
       <c r="B14" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>132477425</v>
       </c>
       <c r="B15" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>132477335</v>
       </c>
       <c r="B16" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 15891-2026 artfynd.xlsx
+++ b/artfynd/A 15891-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132220860</v>
       </c>
       <c r="B2" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132220876</v>
       </c>
       <c r="B3" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>132220852</v>
       </c>
       <c r="B4" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>132220864</v>
       </c>
       <c r="B5" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>132220903</v>
       </c>
       <c r="B6" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>132220808</v>
       </c>
       <c r="B7" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>132398180</v>
       </c>
       <c r="B8" t="n">
-        <v>58632</v>
+        <v>58636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>132398210</v>
       </c>
       <c r="B9" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>132477502</v>
       </c>
       <c r="B10" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>132477732</v>
       </c>
       <c r="B11" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>132477770</v>
       </c>
       <c r="B12" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>132477689</v>
       </c>
       <c r="B13" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>132477468</v>
       </c>
       <c r="B14" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>132477425</v>
       </c>
       <c r="B15" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>132477335</v>
       </c>
       <c r="B16" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 15891-2026 artfynd.xlsx
+++ b/artfynd/A 15891-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132220860</v>
       </c>
       <c r="B2" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132220876</v>
       </c>
       <c r="B3" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>132220852</v>
       </c>
       <c r="B4" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>132220864</v>
       </c>
       <c r="B5" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>132220903</v>
       </c>
       <c r="B6" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>132220808</v>
       </c>
       <c r="B7" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>132398210</v>
       </c>
       <c r="B9" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>132477502</v>
       </c>
       <c r="B10" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>132477770</v>
       </c>
       <c r="B12" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>132477468</v>
       </c>
       <c r="B14" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>132477425</v>
       </c>
       <c r="B15" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>132477335</v>
       </c>
       <c r="B16" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 15891-2026 artfynd.xlsx
+++ b/artfynd/A 15891-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132220860</v>
       </c>
       <c r="B2" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132220876</v>
       </c>
       <c r="B3" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>132220852</v>
       </c>
       <c r="B4" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>132220864</v>
       </c>
       <c r="B5" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>132220808</v>
       </c>
       <c r="B7" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>132398210</v>
       </c>
       <c r="B9" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>132477502</v>
       </c>
       <c r="B10" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>132477770</v>
       </c>
       <c r="B12" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>132477468</v>
       </c>
       <c r="B14" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>132477425</v>
       </c>
       <c r="B15" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>132477335</v>
       </c>
       <c r="B16" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 15891-2026 artfynd.xlsx
+++ b/artfynd/A 15891-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132220860</v>
       </c>
       <c r="B2" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132220876</v>
       </c>
       <c r="B3" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>132220852</v>
       </c>
       <c r="B4" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>132220864</v>
       </c>
       <c r="B5" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>132398210</v>
       </c>
       <c r="B9" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 15891-2026 artfynd.xlsx
+++ b/artfynd/A 15891-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132220860</v>
       </c>
       <c r="B2" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132220876</v>
       </c>
       <c r="B3" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>132220852</v>
       </c>
       <c r="B4" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>132220864</v>
       </c>
       <c r="B5" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>132220903</v>
       </c>
       <c r="B6" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>132220808</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>132398180</v>
       </c>
       <c r="B8" t="n">
-        <v>58636</v>
+        <v>58637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>132398210</v>
       </c>
       <c r="B9" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>132477502</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>132477732</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>132477770</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>132477689</v>
       </c>
       <c r="B13" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>132477468</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>132477425</v>
       </c>
       <c r="B15" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>132477335</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 15891-2026 artfynd.xlsx
+++ b/artfynd/A 15891-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132220860</v>
       </c>
       <c r="B2" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132220876</v>
       </c>
       <c r="B3" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>132220852</v>
       </c>
       <c r="B4" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>132220864</v>
       </c>
       <c r="B5" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>132220903</v>
       </c>
       <c r="B6" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>132220808</v>
       </c>
       <c r="B7" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>132398210</v>
       </c>
       <c r="B9" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>132477502</v>
       </c>
       <c r="B10" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>132477770</v>
       </c>
       <c r="B12" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>132477468</v>
       </c>
       <c r="B14" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>132477425</v>
       </c>
       <c r="B15" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>132477335</v>
       </c>
       <c r="B16" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 15891-2026 artfynd.xlsx
+++ b/artfynd/A 15891-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132220860</v>
       </c>
       <c r="B2" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132220876</v>
       </c>
       <c r="B3" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>132220852</v>
       </c>
       <c r="B4" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>132220864</v>
       </c>
       <c r="B5" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>132220903</v>
       </c>
       <c r="B6" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>132220808</v>
       </c>
       <c r="B7" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>132398210</v>
       </c>
       <c r="B9" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>132477502</v>
       </c>
       <c r="B10" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>132477770</v>
       </c>
       <c r="B12" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>132477468</v>
       </c>
       <c r="B14" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>132477425</v>
       </c>
       <c r="B15" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>132477335</v>
       </c>
       <c r="B16" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 15891-2026 artfynd.xlsx
+++ b/artfynd/A 15891-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132220860</v>
+        <v>132220903</v>
       </c>
       <c r="B2" t="n">
-        <v>101330</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587014</v>
+        <v>587058</v>
       </c>
       <c r="R2" t="n">
-        <v>6432777</v>
+        <v>6432718</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +758,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Större ullticka på liggande död gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,38 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132220876</v>
+        <v>132220926</v>
       </c>
       <c r="B3" t="n">
-        <v>101330</v>
+        <v>91995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -826,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587006</v>
+        <v>587017</v>
       </c>
       <c r="R3" t="n">
-        <v>6432803</v>
+        <v>6432721</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132220852</v>
+        <v>132477689</v>
       </c>
       <c r="B4" t="n">
-        <v>101330</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,41 +921,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Edsbruk, Sm</t>
+          <t>A 15891, Edsbruk, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587078</v>
+        <v>586973</v>
       </c>
       <c r="R4" t="n">
-        <v>6432776</v>
+        <v>6432791</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,22 +983,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,29 +1002,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132220864</v>
+        <v>132477732</v>
       </c>
       <c r="B5" t="n">
-        <v>101330</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,41 +1031,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Edsbruk, Sm</t>
+          <t>A 15891, Edsbruk, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587046</v>
+        <v>586983</v>
       </c>
       <c r="R5" t="n">
-        <v>6432775</v>
+        <v>6432888</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1093,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,67 +1112,79 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132220903</v>
+        <v>132435985</v>
       </c>
       <c r="B6" t="n">
-        <v>91916</v>
+        <v>58131</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>103023</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Edsbruk, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587058</v>
+        <v>587128</v>
       </c>
       <c r="R6" t="n">
-        <v>6432718</v>
+        <v>6432833</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,27 +1211,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Större ullticka på liggande död gran.</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1235,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1239,57 +1253,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132220808</v>
+        <v>132398180</v>
       </c>
       <c r="B7" t="n">
-        <v>99125</v>
+        <v>58658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Edsbruk, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586998</v>
+        <v>587020</v>
       </c>
       <c r="R7" t="n">
-        <v>6432773</v>
+        <v>6432906</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,22 +1330,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,7 +1354,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1359,57 +1372,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132398180</v>
+        <v>132220808</v>
       </c>
       <c r="B8" t="n">
-        <v>58640</v>
+        <v>99195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Edsbruk, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587020</v>
+        <v>586998</v>
       </c>
       <c r="R8" t="n">
-        <v>6432906</v>
+        <v>6432773</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,22 +1449,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,6 +1473,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1478,49 +1492,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132398210</v>
+        <v>132477335</v>
       </c>
       <c r="B9" t="n">
-        <v>101333</v>
+        <v>99195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Edsbruk, Sm</t>
+          <t>A 15891, Edsbruk, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587207</v>
+        <v>586990</v>
       </c>
       <c r="R9" t="n">
-        <v>6432750</v>
+        <v>6432777</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,22 +1569,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,22 +1590,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132477502</v>
+        <v>132477383</v>
       </c>
       <c r="B10" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,10 +1645,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586997</v>
+        <v>586992</v>
       </c>
       <c r="R10" t="n">
-        <v>6432759</v>
+        <v>6432736</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1696,42 +1708,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132477732</v>
+        <v>132477425</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1739,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586983</v>
+        <v>587005</v>
       </c>
       <c r="R11" t="n">
-        <v>6432888</v>
+        <v>6432756</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,17 +1789,13 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1806,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132477770</v>
+        <v>132477468</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,10 +1857,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586949</v>
+        <v>586994</v>
       </c>
       <c r="R12" t="n">
-        <v>6432879</v>
+        <v>6432750</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1912,42 +1920,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132477689</v>
+        <v>132477502</v>
       </c>
       <c r="B13" t="n">
-        <v>57955</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1955,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586973</v>
+        <v>586997</v>
       </c>
       <c r="R13" t="n">
-        <v>6432791</v>
+        <v>6432759</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,17 +2001,13 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2022,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132477468</v>
+        <v>132477770</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586994</v>
+        <v>586949</v>
       </c>
       <c r="R14" t="n">
-        <v>6432750</v>
+        <v>6432879</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,56 +2132,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132477425</v>
+        <v>132220852</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>101403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 15891, Edsbruk, Sm</t>
+          <t>Edsbruk, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587005</v>
+        <v>587078</v>
       </c>
       <c r="R15" t="n">
-        <v>6432756</v>
+        <v>6432776</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2201,12 +2201,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,72 +2232,64 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132477335</v>
+        <v>132220860</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>101403</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 15891, Edsbruk, Sm</t>
+          <t>Edsbruk, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586990</v>
+        <v>587014</v>
       </c>
       <c r="R16" t="n">
         <v>6432777</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2311,12 +2313,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2332,15 +2344,351 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132220864</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Edsbruk, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>587046</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6432775</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132220876</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Edsbruk, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>587006</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6432803</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132398210</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Edsbruk, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>587207</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6432750</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
